--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46070</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>45992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>46162</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>46168</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45771</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44729</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45425</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45293</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45617</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>45569</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44826</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45891</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45884</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45440</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45554</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45632</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45632</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>45994</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44580</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46052</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>46052</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>46070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45632</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45051</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45035</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>46085</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45293</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44508</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44824</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44823</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44740</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>44711</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>44838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44491</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44750</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44907</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45107</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45267</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45764</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45428</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45748</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45251</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45471</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45278</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44992</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45443</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44937</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44846</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45365</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45432</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45750</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45595</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45597</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45545</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45545</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44665</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45264</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44795</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45252</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45425</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45425</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45632</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45069</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45212</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45188</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45188</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>45673</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45108</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45108</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>45331</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45257</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>45670</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45107</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45666</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45632</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45084</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44543</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44826</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45230</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44757</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>46132</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45791</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45639</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45342</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>46041</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44856</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45971</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>46041</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45705</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>46036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>46050</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45891</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45461</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45891</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45890</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>46139</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45890</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45632</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45632</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>45632</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45296</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45896</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45632</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45898</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45899</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45762</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44662</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45747</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>46085</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45183</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45817</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45905</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45905</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45342</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45558</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45960</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>46066</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45265</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46087</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>46024</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45911</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45279</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46108</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>46043</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45580</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>46030</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45597</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>46098</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45040</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45254</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45891</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>44837</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45562</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45393</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45243</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45093</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45929</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>46142</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45677</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46142</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45510</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45754</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46146</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45972</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>46024</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45398</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45548</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45936</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46147</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46141</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46146</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>46149</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45426</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>45597</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45944</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>46148</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>46149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>46148</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>46149</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>46087</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45761</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45754</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45748</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45954</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45526</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45597</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45957</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>46150</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>44938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45960</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45706</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45960</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45964</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45600</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45548</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45967</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45062</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45966</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45170</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45967</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45394</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>46076</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45327</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46155</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45972</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45750</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45975</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45961</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45979</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45461</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>46155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45982</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45982</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45527</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>46157</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46157</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45985</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>46157</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>46157</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>46157</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44651</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>46157</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>46101</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>46157</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45028</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45992</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>44508</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>44649</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45012</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45373</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45607</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45628</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>46163</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45622</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45622</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45602</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45561</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>46162</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46163</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45995</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45985</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45999</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45999</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>46000</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>46001</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>46167</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>46164</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45747</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>46001</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>46164</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45762</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46165</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45202</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45604</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45775</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45764</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>46007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45467</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45936</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45027</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>46112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45796</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>46008</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45574</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>46168</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>46097</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45056</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45621</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45098</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>44963</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>46026</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>46026</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45567</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>46026</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>46029</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45750</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45750</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>46030</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>44957</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45707</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>46034</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46034</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>46035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>46024</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45251</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>46034</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>46035</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>46024</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>46035</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>46024</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>46037</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>46174</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>46174</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>46174</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>46036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46036</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>46037</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>46037</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45246</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>46174</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>46041</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44546</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>46043</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45632</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45062</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>46045</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46044</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45113</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45593</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>46175</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>46055</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45425</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>45588</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>46052</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>46055</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>44824</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>46055</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>46052</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>46043</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45565</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46177</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45566</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>46058</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45707</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44897</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46063</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46062</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46062</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44869</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45246</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>46063</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>46063</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46062</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46063</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46177</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46066</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>46069</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>46155</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>46066</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46177</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46066</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>46066</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46069</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46182</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45616</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46070</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46181</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46073</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45222</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46077</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>46076</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46076</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45324</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>46076</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>46076</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>46079</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45219</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>46188</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46185</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>46085</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>46085</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>46087</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45260</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>46093</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45470</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>46093</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>46094</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>46122</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45754</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>46098</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>46062</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46099</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>46099</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>44564</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46099</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46099</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46104</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46104</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46163</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>46106</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46197</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46108</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46197</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45677</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45243</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45757</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>46111</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>46112</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45041</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46112</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46112</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46113</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46117</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>46117</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46117</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>46117</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45215</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45580</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45560</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45560</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45107</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>44460</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>46094</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>44992</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45398</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>44490</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>46127</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46133</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46132</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46132</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>44760</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46135</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45764</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45278</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46135</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45453</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44739</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>46029</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>46093</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>46093</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>46136</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>46062</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46087</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>46078</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>46058</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>44582</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45905</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45747</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45544</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45093</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45722</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44956</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45560</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45639</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44992</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46207</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>45477</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>45096</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>46253</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46252</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>46253</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45231</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>46252</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45108</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45476</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45597</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45432</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44823</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45602</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46212</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46212</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46212</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>46212</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45770</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>46211</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45108</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45609</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>45595</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45771</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>46258</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>46258</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45590</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>45705</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>46042</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45799</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45327</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45797</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>46260</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>46260</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45435</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>46218</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>46219</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>46219</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45534</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45594</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46219</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>46219</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>46223</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>45764</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45113</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>46267</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45600</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>45749</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>46268</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45779</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46272</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>46227</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45544</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45588</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>46275</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45149</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45420</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>46281</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>46048</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>46237</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45791</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45791</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45791</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>46147</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>46085</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>44698</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45527</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45442</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45467</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>44776</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45798</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45799</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45643</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45428</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45805</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45805</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45272</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>44883</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45810</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45762</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45821</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45824</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45824</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45826</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45825</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45600</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45436</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45817</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>45847</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45848</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>45848</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>45863</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45867</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45811</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45879</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45879</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45821</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>45883</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45293</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>44566</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>44566</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44566</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45973</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45994</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45210</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>46070</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44729</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45771</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45293</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45891</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46052</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45509</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45035</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45992</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45994</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45994</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45554</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>45632</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>45632</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44826</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>46085</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44580</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45632</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>45569</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45440</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45293</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44508</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44824</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44823</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44740</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>44711</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>44838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44491</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45698</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45327</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45183</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44856</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45342</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45215</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>45754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45425</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45750</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44823</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45373</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45428</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45278</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45527</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45442</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>46026</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>45597</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>46026</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>46029</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>45545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45279</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>46030</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45467</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45443</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45643</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45798</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45544</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44776</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45467</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45884</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>46024</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45432</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45707</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>46034</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>46035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>46035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46024</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45890</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>46035</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>46037</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45471</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45891</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>46037</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45891</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45898</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46043</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>46045</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45762</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45899</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45545</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44897</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>46052</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45905</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>46052</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45476</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>46055</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>46055</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45911</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46062</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45604</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>46062</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45428</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46063</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>46063</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>46063</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>46063</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>46066</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46066</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>46066</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46070</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45891</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46069</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>46076</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46076</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45805</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>46073</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>46076</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46077</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44582</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>46079</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45929</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44869</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45107</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45805</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44883</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45272</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46085</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46087</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45936</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45810</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45324</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45594</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>46093</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>46093</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45944</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>46094</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>46099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45943</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>46099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>46098</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>46099</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46099</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45762</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45398</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45526</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46104</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45093</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>46104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45251</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45954</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46108</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>46111</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46112</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>46112</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46113</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46112</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45957</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45957</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44956</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>46117</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46117</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>46117</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46117</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45426</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45960</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45574</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45609</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45609</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45621</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45597</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45966</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46094</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45967</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45967</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45972</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45974</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44490</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45754</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46132</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45961</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45975</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45275</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46132</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45979</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45398</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45548</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45979</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>46133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45982</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45982</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46093</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45632</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46135</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45985</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45985</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45985</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44649</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>46135</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44757</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46093</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46029</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45905</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44795</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45992</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>46058</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>46062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45666</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46108</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46087</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>46087</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46000</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45764</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>46041</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46001</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45246</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45219</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>44837</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>46001</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46041</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46132</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45705</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>46007</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44739</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46008</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45749</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46066</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45960</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44824</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45670</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45762</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44846</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45796</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>46078</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45817</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45821</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45677</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45558</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>46036</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45824</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45791</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45757</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45170</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46044</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45824</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45971</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46024</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>46043</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>46043</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>46085</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>46136</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>46139</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45826</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45750</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45750</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>46030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46098</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>46142</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>46142</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>46097</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>46024</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44760</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46146</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45548</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45972</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>46146</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45600</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>46141</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>46148</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>46148</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>46147</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>46087</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46149</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>46150</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>46149</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>46149</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44895</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45764</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>46155</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45453</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46155</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>46076</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>46157</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46157</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46157</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46157</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46157</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46157</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>46157</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46162</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45636</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45251</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45264</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44992</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44907</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46163</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45436</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45084</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>46164</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45107</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45817</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>46164</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45560</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45560</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>46163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45848</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45936</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46167</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45847</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45848</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>46165</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46112</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46035</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46168</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>46097</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45574</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45107</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>45062</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45600</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45096</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>46174</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45863</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45028</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>46175</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46174</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>46174</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>46174</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>46174</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45461</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>46177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45867</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>46177</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44938</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46043</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45040</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45593</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45616</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45210</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>46181</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45212</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>46177</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>46155</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45761</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45365</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46182</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45108</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45108</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45251</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>46185</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>44564</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45027</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>46122</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45607</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>45622</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>45580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>45670</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45754</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45056</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>46062</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45615</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>46197</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45590</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46163</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>45879</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>46197</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45879</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45821</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45632</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45639</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45597</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45706</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45747</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45331</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44812</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>46252</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>46252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46207</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45597</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45222</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45639</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46211</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45567</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>46253</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46253</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>45432</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46258</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>46212</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>46212</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46212</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46212</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>45799</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45113</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45705</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>46258</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45670</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>46260</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46260</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>46042</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45188</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45188</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>44662</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>46219</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46219</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44750</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46218</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46219</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>46219</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45257</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45267</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46223</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46268</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45477</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46267</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>46227</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46275</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46048</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>46085</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46237</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>46147</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45602</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45652</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45393</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46281</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45510</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45461</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45425</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46026</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>45749</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45534</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45561</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45560</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>44992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44957</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45230</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>44665</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>44651</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45108</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45041</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44963</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45764</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45231</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45597</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45243</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45632</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45632</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45470</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>44543</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45278</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45342</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45632</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45747</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45600</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>44508</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45527</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45435</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45628</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45677</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>45673</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45632</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45771</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45098</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45062</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>44826</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45588</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45580</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45252</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45215</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45108</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45747</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45595</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45595</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45394</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>45562</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45770</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45750</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45602</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45622</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45219</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45748</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45069</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45296</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45327</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45707</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45632</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45615</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45265</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45779</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45420</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>45588</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>45544</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45149</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45791</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45791</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>45791</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>44566</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>44566</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>44566</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45293</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>45973</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45509</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45994</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45210</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>46070</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44729</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45771</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45293</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45891</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46052</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45509</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45035</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45992</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45994</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45994</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45554</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>45632</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>45632</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44826</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>46085</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44580</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45632</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>45569</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45440</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45293</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44508</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44824</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44823</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44740</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>44711</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>44838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44491</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45698</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45327</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45183</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44856</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45342</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45215</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>45754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45425</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45750</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44823</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45373</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45428</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45278</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45527</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45442</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>46026</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>45597</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>46026</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>46029</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>45545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45279</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>46030</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45467</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45443</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45643</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45798</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45544</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44776</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45467</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45884</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>46024</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45432</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45707</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>46034</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>46035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>46035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46024</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45890</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>46035</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>46037</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45471</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45891</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>46037</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45891</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45898</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46043</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>46045</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45762</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45899</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45545</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44897</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>46052</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45905</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>46052</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45476</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>46055</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>46055</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45911</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46062</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45604</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>46062</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45428</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46063</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>46063</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>46063</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>46063</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>46066</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46066</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>46066</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46070</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45891</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46069</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>46076</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>46076</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46076</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45805</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>46073</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>46076</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46077</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44582</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>46079</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45929</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44869</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45107</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45805</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44883</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45272</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46085</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46087</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45936</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45810</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45324</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45594</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>46093</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>46093</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45944</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>46094</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>46099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45943</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>46099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>46098</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>46099</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46099</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45762</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45398</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45526</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46104</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45093</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>46104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45251</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45954</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46108</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>46111</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46112</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>46112</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46113</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46112</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45957</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45957</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44956</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>46117</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46117</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>46117</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46117</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45426</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45960</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45574</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45609</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45609</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45621</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45597</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45966</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46094</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45967</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45967</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45972</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45972</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45974</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44490</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45754</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46132</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45961</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45975</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45275</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46132</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45979</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45398</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45548</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45979</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>46133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45982</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45982</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46093</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45632</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46135</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45985</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45985</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45985</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44649</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>46135</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44757</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46093</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46029</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45905</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44795</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45992</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>46058</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>46062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45666</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46108</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46087</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>46087</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46000</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45764</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>46041</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46001</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45246</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45219</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>44837</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>46001</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46041</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46132</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45705</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>46007</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44739</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46008</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45749</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46066</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45960</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44824</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45670</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45762</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44846</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45796</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>46078</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45817</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45821</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45677</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45558</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>46036</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45824</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45791</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45757</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45170</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46044</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45824</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45971</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46024</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>46043</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>46043</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>46085</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>46136</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>46139</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45826</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45750</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45750</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>46030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46098</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>46142</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>46142</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>46097</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>46024</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44760</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46146</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45548</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45972</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>46146</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45600</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>46141</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>46148</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>46148</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>46147</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>46087</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46149</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>46150</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>46149</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>46149</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44895</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45764</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>46155</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45453</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46155</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>46076</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>46157</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46157</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46157</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46157</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46157</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46157</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>46157</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46162</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45636</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45251</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45264</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44992</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44907</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46163</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45436</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45084</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>46164</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45107</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45817</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>46164</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45560</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45560</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>46163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45848</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45936</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46167</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45847</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45848</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>46165</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46112</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46035</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46168</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>46097</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45574</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45107</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>45062</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45600</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45096</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>46174</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45863</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45028</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>46175</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46174</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>46174</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>46174</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>46174</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45461</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>46177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45867</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>46177</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44938</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46043</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45040</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45593</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45616</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45210</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>46181</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45212</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>46177</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>46155</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45761</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45365</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46182</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45108</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45108</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45251</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>46185</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>44564</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45027</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>46122</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45607</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>45622</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>45580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>45670</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45754</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45056</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>46062</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45615</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>46197</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45590</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46163</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>45879</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>46197</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45879</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45821</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45632</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45639</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45597</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45706</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45747</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45331</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44812</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>46252</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>46252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46207</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45597</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45222</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45639</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46211</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45567</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>46253</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46253</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>45432</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46258</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>46212</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>46212</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46212</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46212</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>45799</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45113</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45705</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>46258</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45670</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>46260</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46260</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>46042</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45188</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45188</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>44662</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>46219</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>46219</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44750</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46218</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46219</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>46219</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45257</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45267</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46223</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46268</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45477</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46267</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>46227</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46275</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46048</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>46085</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46237</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>46147</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45602</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45652</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45393</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46281</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45510</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45461</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45425</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46026</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>45749</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45534</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45561</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45560</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>44992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44957</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45230</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>44665</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>44651</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45108</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45041</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44963</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45764</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45231</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45597</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45243</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45632</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45632</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45470</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>44543</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45278</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45342</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45632</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45747</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45600</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>44508</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45527</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45435</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45628</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45677</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>45673</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45632</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45771</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45098</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45062</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>44826</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45588</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45580</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45252</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45215</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45108</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45747</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45595</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45595</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45394</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>45562</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45770</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45750</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45602</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45622</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45219</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45748</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45069</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45296</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45327</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45707</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45632</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45615</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45265</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45779</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45420</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>45588</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>45544</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45149</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45791</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45791</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>45791</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>44566</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>44566</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>44566</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45293</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>45973</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45798</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45994</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45905</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45992</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>46070</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46162</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46168</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>44729</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>46296</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45771</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45293</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45617</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45884</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45891</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46052</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>45569</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>45629</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44826</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45992</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45994</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45994</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45440</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45632</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>45632</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44580</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46085</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45051</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45035</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45293</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44508</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44837</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44824</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44823</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44740</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44711</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44491</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44750</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44907</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45267</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45428</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45748</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45764</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45251</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45278</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44992</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45471</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>44937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45443</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45884</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45652</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>46007</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>46008</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>45791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45615</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45891</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45891</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>46026</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45890</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45890</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>46026</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45432</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>46029</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45896</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45750</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>46030</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45595</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45898</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45707</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45899</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45762</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>46034</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>46024</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>46035</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>46024</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>46037</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45597</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45905</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>46036</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>46037</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45905</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>46037</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46041</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>46043</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45911</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44698</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45527</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45442</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45911</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>46045</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44665</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45545</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45545</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45467</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44776</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45799</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45252</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45212</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45428</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45805</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46055</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45264</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45891</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46052</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>46055</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46055</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>46052</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46058</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45929</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45272</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44795</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46063</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>46062</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45425</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45425</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45632</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46063</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46063</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>46062</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46063</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>46066</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46069</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46066</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45251</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45936</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>46066</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>46066</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46069</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46070</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>46073</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44883</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45810</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>46077</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>46076</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45944</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46076</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>46076</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45188</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45673</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45762</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45954</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45957</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45957</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46085</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45008</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45670</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45960</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45960</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46087</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45960</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45960</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45960</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45108</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>46093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46093</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>45331</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45257</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45966</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>46094</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45966</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45670</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46098</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45219</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45972</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46099</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45230</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46099</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46099</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>46104</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45975</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45632</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44812</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>46104</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45107</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45666</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45084</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45961</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45978</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>46108</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45757</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45982</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>46111</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>46112</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45982</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>46112</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44826</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45985</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45821</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>46113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>46117</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45824</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>46117</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>46117</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>46117</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45992</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45992</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44895</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44757</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45639</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45985</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45342</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45826</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45999</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45825</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>46094</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46000</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>44856</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45398</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>44490</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45275</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>46127</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46001</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45705</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>46133</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>46001</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46132</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45600</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>46132</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45698</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46135</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45461</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>46135</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45215</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46029</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>46093</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>46093</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45632</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45632</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46136</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>46062</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46087</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>46058</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45632</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45905</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45436</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44662</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45747</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45183</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45342</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45817</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45791</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>46041</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45847</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45265</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45848</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45971</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45848</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>46041</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45279</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46050</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45580</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45597</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45040</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>46139</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>44837</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46043</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45562</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45393</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45243</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>46085</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45093</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45817</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45558</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45960</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45677</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>46066</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45545</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46087</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>45510</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46024</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45754</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>46097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45863</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45398</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45867</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>46108</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>46043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45811</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45426</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>46030</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>46098</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45597</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45757</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46142</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>46142</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>46146</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45972</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>46024</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45548</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>46147</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>46141</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45761</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>46146</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45615</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45754</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45748</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45670</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46149</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45526</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45597</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>46148</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44938</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46149</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>46148</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>46149</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>46087</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46150</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45706</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45600</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>46076</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>46155</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45548</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45170</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>46155</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>45394</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>46157</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46157</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>46157</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>46157</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>46157</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>45327</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>46157</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46101</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>46157</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45750</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>46163</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>46162</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>46163</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46167</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>46164</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>45461</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46165</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45936</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>46112</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45527</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45879</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>46168</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>46035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>46097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>44651</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45879</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>46174</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>46174</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>46174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45821</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>46174</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45028</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44508</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>46174</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>46174</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45883</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44649</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45012</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45373</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>46175</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45607</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45628</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>46177</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>46177</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45622</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45622</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46155</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>46177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45602</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>46182</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45210</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>45561</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>46181</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>46185</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45747</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45762</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>46122</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45604</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>45775</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45764</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45467</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45027</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>46062</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45574</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>46197</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>46197</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>45056</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45621</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44963</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45567</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45750</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45750</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>44957</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45251</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46207</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45246</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>44546</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>46212</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45632</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46212</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>46212</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46212</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45062</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>46258</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46042</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45799</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45593</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>46260</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>46218</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45425</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45588</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>44824</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46219</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45565</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45566</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46219</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>45707</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44897</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46219</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46219</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44869</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45246</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>46223</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>46267</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45616</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>46268</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45222</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45324</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>46272</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>46227</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45219</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>46275</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>46281</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>46048</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>46237</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>46147</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46085</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45260</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45470</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45754</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45609</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44564</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45677</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45243</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46026</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45215</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45580</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>46293</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45560</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45560</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45107</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44992</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46293</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>46293</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>44760</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>46163</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>46078</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45764</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45278</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45453</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>44739</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>46252</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>46252</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>46294</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>46294</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>44582</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45747</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45544</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45093</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45722</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>46296</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>44956</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>46296</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>45560</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>46296</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>46295</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>46296</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45639</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>46253</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>44992</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>46296</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>46253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45477</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>45096</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45231</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45108</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45476</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45597</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45432</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>44823</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45602</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45770</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45108</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45609</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45595</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45771</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45590</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45705</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45327</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45435</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45534</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45594</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45764</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45113</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45600</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45749</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45779</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45544</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45588</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>45149</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45420</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45293</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44566</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>44566</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>44566</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45973</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45798</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45994</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45905</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45992</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>46070</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46162</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46168</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>44729</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>46296</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45771</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45293</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45617</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45884</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45891</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46052</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46070</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>45569</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>45629</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44826</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45992</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45825</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45994</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45994</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45440</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45632</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>45632</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44580</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46085</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45051</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45035</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45293</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44508</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44837</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44824</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44616</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44823</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44740</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44711</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44491</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44750</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44907</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45267</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45428</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45748</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45764</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45251</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45278</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44992</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45471</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>44937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45443</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45884</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45652</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>46007</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>46008</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>45791</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45615</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45891</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45891</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>46026</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45890</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45890</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>46026</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45432</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>46029</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45896</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45750</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>46030</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45595</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45898</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45707</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45899</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45762</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>46034</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>46024</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>46035</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>46024</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>46037</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45597</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45905</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>46036</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>46037</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45905</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>46037</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>46041</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>46043</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45911</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44698</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45527</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45442</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45911</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>46045</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44665</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45545</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45545</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45467</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44776</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45799</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45252</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45212</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45428</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45805</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46055</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45264</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45891</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46052</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>46055</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46055</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>46052</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46058</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45929</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45272</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44795</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46063</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>46062</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45425</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45425</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45632</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46063</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46063</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>46062</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46063</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>46066</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46069</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46066</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45251</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45936</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>46066</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>46066</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46069</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46070</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>46073</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44883</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45810</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>46077</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>46076</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45944</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46076</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>46076</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45188</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45673</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45762</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45954</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45957</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45957</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46085</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45008</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45670</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45960</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45960</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46087</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45960</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45960</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45960</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45108</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>46093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46093</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>45331</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45257</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45966</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>46094</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45966</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45670</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46098</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45219</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45972</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46099</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45230</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>46099</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46099</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>46104</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45975</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45632</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44812</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>46104</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45107</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45666</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45084</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45961</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45978</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>46108</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45757</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45982</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>46111</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>46112</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45982</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>46112</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44826</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45985</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45821</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>46113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>46117</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45824</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>46117</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>46117</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>46117</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45992</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45992</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44895</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44757</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45639</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45985</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45342</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45826</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45999</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45825</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>46094</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46000</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>44856</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45398</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>44490</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45275</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>46127</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46001</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45705</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>46133</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>46001</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46132</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45600</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>46132</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45698</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46135</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45461</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>46135</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45215</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46029</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>46093</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>46093</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45632</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45632</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46136</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>46062</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46087</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>46058</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45632</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45905</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45436</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44662</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45747</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45183</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45342</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45817</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45791</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>46041</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45847</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45265</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45848</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45971</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45848</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>46041</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45279</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46050</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45580</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45597</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45040</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>46139</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>44837</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46043</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45562</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45393</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45243</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>46085</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45093</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45817</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45558</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45960</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45677</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>46066</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45545</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46087</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>45510</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46024</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45754</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>46097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45863</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45398</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45867</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>46108</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>46043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45811</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45426</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>46030</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>46098</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45597</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45757</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46142</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>46142</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>46146</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45972</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>46024</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45548</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>46147</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>46141</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45761</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>46146</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45615</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45754</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45748</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45670</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46149</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45526</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45597</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>46148</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44938</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46149</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>46148</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>46149</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>46087</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46150</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45706</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45600</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>46076</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>46155</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45548</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45170</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>46155</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>45394</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>46157</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46157</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>46157</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>46157</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>46157</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>45327</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>46157</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46101</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>46157</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45750</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>46163</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>46162</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>46163</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46167</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>46164</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>45461</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46165</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45936</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>46112</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45527</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45879</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>46168</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>46035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>46097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>44651</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45879</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>46174</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>46174</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>46174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45821</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>46174</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45028</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44508</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>46174</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>46174</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45883</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44649</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45012</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45373</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>46175</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45607</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45628</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>46177</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>46177</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45622</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45622</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46155</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>46177</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45602</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>46182</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45210</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>45561</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>46181</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>46185</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45747</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45762</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>46122</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45604</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>45775</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45764</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45467</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45027</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>46062</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45574</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>46197</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>46197</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>45056</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45621</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44963</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45567</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45750</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45750</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>44957</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45251</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46207</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45246</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>44546</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>46212</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45632</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46212</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>46212</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46212</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45062</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>46258</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46042</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45799</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45593</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>46260</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>46218</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45425</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45588</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>44824</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46219</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45565</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45566</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46219</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>45707</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44897</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46219</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46219</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44869</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45246</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>46223</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>46267</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45616</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>46268</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45222</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45324</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>46272</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>46227</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45219</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>46275</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>46281</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>46048</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>46237</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>46147</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>46085</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45260</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45470</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45754</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45609</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44564</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45677</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45243</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46026</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45215</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45580</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>46293</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45560</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45560</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45107</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44992</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46293</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>46293</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>44760</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>46163</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>46078</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45764</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45278</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45453</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>44739</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>46252</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>46252</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>46294</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>46294</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>44582</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45747</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45544</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45093</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45722</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>46296</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>44956</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>46296</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>45560</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>46296</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>46295</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>46296</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45639</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>46253</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>44992</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>46296</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>46253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45477</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>45096</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45231</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45108</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45476</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45597</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45432</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>44823</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45602</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45770</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45108</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45609</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45595</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45771</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45590</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45705</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45327</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45435</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45534</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45594</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45764</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45113</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45600</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45749</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45779</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45544</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45588</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>45149</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45420</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45293</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44566</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>44566</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>44566</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45973</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45798</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45994</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>46070</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>46162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46296</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45293</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45632</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45617</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45884</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45891</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45569</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45440</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45554</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45632</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45632</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45035</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45051</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45992</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45994</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44580</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46052</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>46085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45293</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44686</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44637</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44837</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44824</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44616</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44820</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44838</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44783</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44663</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44491</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45113</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44508</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45425</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45527</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45202</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45764</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45008</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45750</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45215</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45435</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45373</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45428</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45453</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>45698</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45565</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44823</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45327</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>45636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45251</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45632</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45264</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45771</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44907</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44856</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45084</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45425</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>45342</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45062</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44826</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45560</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45754</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45580</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45252</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45215</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45108</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45747</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44546</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45595</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45595</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45394</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45562</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45883</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45770</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45750</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45622</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45278</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45107</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>45219</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45597</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45545</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45545</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45748</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45279</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45600</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45467</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45890</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45443</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45296</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45096</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45012</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45544</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45028</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45890</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45891</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45891</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45896</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45898</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45432</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45327</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45762</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45246</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45899</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45471</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45707</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45461</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44938</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45040</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45905</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45265</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45905</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45593</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45616</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45212</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45779</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45761</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45365</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45545</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45420</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45108</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45108</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45476</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45251</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45588</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44564</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45027</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45604</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45544</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45607</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45622</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45580</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45670</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45748</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45791</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45056</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45791</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45615</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45929</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45791</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44582</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45590</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45929</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>44937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45527</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45442</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45107</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>44698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45632</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45639</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45597</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45643</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45798</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44776</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45467</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45324</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45706</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45747</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45936</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45799</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45594</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45428</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45937</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45331</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45805</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45805</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45398</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44883</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45526</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45093</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45597</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45272</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45222</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45810</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45251</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45639</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45762</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45943</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45432</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44956</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45426</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45574</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45821</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45609</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45609</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45824</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45621</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45113</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45705</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45825</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45826</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>45597</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>45670</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45957</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45960</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45960</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45754</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45188</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44662</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45964</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44750</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45764</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45966</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45966</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45548</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45966</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45967</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45967</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45632</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45257</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44649</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45972</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44757</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45436</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45972</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>45817</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45267</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>44795</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45848</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45848</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45974</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45666</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45978</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45978</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45722</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45477</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45863</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45975</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45811</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45219</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45867</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44837</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45979</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45705</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44739</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45749</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44824</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45670</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45979</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45762</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>44846</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45982</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45879</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45677</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45879</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45821</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45243</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45982</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45170</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46094</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46099</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46099</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>46098</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>46099</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46099</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45750</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45750</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45985</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46104</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45602</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>46104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45652</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45393</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46106</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45510</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46108</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45757</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45461</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45425</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>46111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45992</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>46112</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45992</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>46112</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44760</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46112</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46117</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>46117</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>46117</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>46117</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45749</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45999</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45999</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45999</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>46000</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>46127</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44490</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46001</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>46132</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45534</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45561</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45275</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44992</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46132</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45560</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45398</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>46001</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>46133</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>46093</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>46135</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>46135</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46007</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>46008</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45230</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46093</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45905</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>44665</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45796</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46058</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>46062</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>44651</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45108</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>46108</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>46087</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>46087</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>46026</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>46026</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45041</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>46029</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>46041</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>46030</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44963</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45764</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45231</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46041</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>46132</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46024</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>46024</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>46034</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45597</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46036</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>46066</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>46035</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45243</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45960</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45632</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45632</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>46035</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45470</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>46024</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>46035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44543</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>46036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>46037</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>46037</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>46037</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45278</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>46041</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45817</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>46043</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46044</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45558</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45342</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>46036</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45791</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45757</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45632</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46044</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>45971</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46024</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46043</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45747</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46043</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>46085</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46136</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>46045</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46050</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46139</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45600</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46030</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>46052</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>46052</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46055</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>46055</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>46055</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>46058</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46142</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>46142</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>46062</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>46097</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>46062</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>46062</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>46024</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>46063</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45548</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
         <v>46063</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>46063</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>46063</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45972</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>46066</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46146</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>46066</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46066</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46066</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46141</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46148</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46069</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46148</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46147</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>46087</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>46070</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>46149</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>46150</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46149</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46069</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46149</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46076</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>46076</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>46073</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46076</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>46077</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46079</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>46155</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46155</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>46076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46085</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46085</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46087</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>46101</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>46157</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>46157</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46157</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>46157</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>46157</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46157</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46157</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46093</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>46162</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>46093</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>46163</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46164</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>46164</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46163</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45936</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>46167</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>46165</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>46112</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>46035</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>46168</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>46097</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>46174</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>46175</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>46174</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>46174</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>46174</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>46174</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46174</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>46177</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>46177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>46043</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45210</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46181</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46182</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46185</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>46122</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>46062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>46197</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>46197</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>46207</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46211</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46212</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>46212</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>46212</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>46212</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45799</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>46042</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>46219</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>46219</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>46219</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>46219</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>46223</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46268</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46267</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>46272</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>46227</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>46275</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>46048</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>46237</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>46147</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>46281</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>46026</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>46078</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>46294</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>46293</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>46293</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>46293</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46163</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46296</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>46296</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>46252</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>46252</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>46296</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>46253</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>46296</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>46296</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>46085</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>46253</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>46295</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>46155</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>46302</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>46301</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>46034</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>46177</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>46258</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>46258</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>46303</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>46034</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46218</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>46303</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46304</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>46260</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>46303</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>46260</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>46304</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>46303</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>44566</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>44566</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>44566</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45293</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45973</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45798</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45994</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>46070</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>46162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46168</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46296</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45293</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45632</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45617</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45884</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45891</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45569</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45440</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45554</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45632</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45825</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45632</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45035</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45051</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45992</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45994</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44580</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46052</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>46085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45293</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44686</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44637</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44837</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44824</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44616</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44820</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44838</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44783</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44663</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44491</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45113</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44508</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45425</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45527</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45202</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45764</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45008</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45750</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45215</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45435</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45373</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45428</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45453</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45677</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>45698</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45565</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44823</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45327</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>45636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45251</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45632</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45264</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45771</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44907</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44856</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45084</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45425</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>45342</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45062</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44826</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45560</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45754</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45580</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45252</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45215</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45108</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45747</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44546</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45595</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45595</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45394</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45562</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45883</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45770</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45750</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45622</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45278</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45107</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>45219</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45597</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45545</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45545</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45748</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45279</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45600</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45467</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45890</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45443</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45296</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45096</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45012</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45544</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45028</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45890</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45891</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45891</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45896</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45898</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45432</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45327</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45762</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45246</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45899</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45471</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45707</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45461</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44938</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45040</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45905</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45265</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45905</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45593</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45616</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45212</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45779</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45761</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45365</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45911</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45545</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45420</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45108</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45108</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45476</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45251</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45588</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44564</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45027</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45604</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45544</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45607</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45622</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45580</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45670</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45748</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45791</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45056</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45791</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45615</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45929</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45791</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44582</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45590</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45929</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>44937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45527</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45442</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45107</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>44698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45632</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45639</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45597</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45643</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45798</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44776</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45467</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45324</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45706</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45747</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45936</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45799</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45594</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45428</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45937</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45331</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45805</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45805</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45398</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44883</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45526</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45093</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45597</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45272</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45222</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45810</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45251</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45639</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45762</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45943</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45432</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44956</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45426</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45574</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45821</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45609</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45609</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45824</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45621</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45113</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45705</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45825</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45826</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>45597</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>45670</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45957</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45960</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45960</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45754</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45188</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44662</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45964</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44750</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45764</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45966</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45966</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45548</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45966</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45967</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45967</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45632</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45257</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44649</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45972</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44757</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45436</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45972</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>45817</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45267</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>44795</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45848</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45848</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45974</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45666</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45978</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45978</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45722</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45477</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45863</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45975</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45811</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45219</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45867</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44837</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45979</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45705</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44739</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45749</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44824</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45670</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45979</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45762</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>44846</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45982</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45879</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45677</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45879</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45821</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45243</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45982</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45170</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46094</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46099</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46099</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>46098</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>46099</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46099</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45750</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45750</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45985</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46104</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45602</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>46104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45652</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45393</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46106</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45510</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46108</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45757</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45461</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45425</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>46111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45992</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>46112</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45992</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>46112</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44760</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46112</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46117</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>46117</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>46117</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>46117</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45749</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45999</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45999</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45999</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>46000</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>46127</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>44490</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46001</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>46132</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45534</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45561</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45275</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44992</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46132</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45560</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45398</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>46001</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>46133</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>46093</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>46135</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>46135</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46007</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>46008</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45230</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46093</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45905</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>44665</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45796</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46058</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>46062</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>44651</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45108</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>46108</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>46087</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>46087</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>46026</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>46026</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45041</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>46029</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>46041</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>46030</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44963</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45764</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45231</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46041</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>46132</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46024</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>46024</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>46034</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45597</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>46036</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>46066</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>46035</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45243</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45960</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45632</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45632</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>46035</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45470</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>46024</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>46035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44543</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>46036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>46037</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>46037</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>46037</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45278</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>46041</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45817</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>46043</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46044</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45558</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45342</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>46036</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45791</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45757</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45632</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46044</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>45971</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46024</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46043</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45747</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46043</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>46085</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46136</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>46045</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46050</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46139</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45600</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46030</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>46052</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>46052</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46055</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>46055</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>46055</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>46058</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46142</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>46142</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>46062</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>46097</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>46062</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>46062</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>46024</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>46063</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45548</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
         <v>46063</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>46063</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>46063</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45972</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>46066</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46146</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>46066</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46066</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46066</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46141</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46148</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46069</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46148</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46147</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>46087</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>46070</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>46149</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>46150</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46149</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46069</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46149</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46076</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>46076</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>46073</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46076</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>46077</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46079</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>46155</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46155</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>46076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46085</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46085</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46087</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>46101</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>46157</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>46157</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46157</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>46157</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>46157</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46157</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46157</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46093</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>46162</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>46093</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>46163</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46164</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>46164</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46163</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45936</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>46167</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>46165</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>46112</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>46035</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>46168</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>46097</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>46174</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>46175</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>46174</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>46174</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>46174</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>46174</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46174</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>46177</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>46177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>46043</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45210</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46181</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46182</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46185</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>46122</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>46062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>46197</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>46197</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>46207</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46211</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46212</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>46212</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>46212</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>46212</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45799</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>46042</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>46219</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>46219</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>46219</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>46219</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>46223</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46268</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46267</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>46272</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>46227</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>46275</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>46048</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>46237</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>46147</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>46281</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>46026</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>46078</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>46294</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>46293</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>46293</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>46293</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46163</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46296</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>46296</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>46252</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>46252</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>46296</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>46253</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>46296</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>46296</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>46085</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>46253</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>46295</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>46155</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>46302</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>46301</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>46034</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>46177</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>46258</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>46258</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>46303</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>46034</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46218</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>46303</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46304</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>46260</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>46303</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>46260</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>46304</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>46303</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>44566</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>44566</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>44566</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45293</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45973</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>46070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>46162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46168</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>46296</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45425</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45293</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45617</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45569</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>44826</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45891</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45884</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>45972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45440</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>45509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45554</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45992</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45994</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45994</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45632</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45632</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46052</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>46070</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44580</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45632</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>46052</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45035</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>46085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45825</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45293</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44686</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44837</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44740</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44783</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44820</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44837</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44663</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44838</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44698</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44491</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44750</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>45267</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45107</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44907</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>45428</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45764</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45471</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44937</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45443</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44846</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44992</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45365</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45750</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45432</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45595</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45597</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44665</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45212</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45264</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44795</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45251</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45069</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45673</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>45008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45425</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45425</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45108</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45108</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45331</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45257</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45230</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45107</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45666</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45084</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45632</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44543</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44826</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>46132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45791</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46041</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46041</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>46036</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46044</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>46050</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44757</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45639</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>46139</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45342</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45891</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45891</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45890</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45890</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44856</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>46043</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45896</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45698</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>46085</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45884</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45898</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45558</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45960</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46066</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>46087</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>46024</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>46097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45899</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>45461</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>46108</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>46043</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45762</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>46030</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>46098</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45905</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45215</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45905</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45632</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45632</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45632</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45296</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45757</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45632</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>46142</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>46142</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>46146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45972</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>46024</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45548</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44662</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45747</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45342</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>46147</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>46141</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>46146</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46149</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45279</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45580</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>46148</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46148</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46149</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>45929</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>46087</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45597</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45040</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>46150</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45936</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45937</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45254</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>44837</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45562</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45393</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45243</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45943</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45093</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45944</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45677</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45545</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>46076</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45510</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46155</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45754</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45398</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45954</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>46155</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>46157</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46157</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46157</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46157</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>46157</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>46157</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>46101</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46157</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45960</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45960</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45960</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45426</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45597</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45967</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45966</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45967</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45966</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45972</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>46163</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45975</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45761</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>45615</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45748</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45670</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45974</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45526</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45597</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45961</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>44938</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>46162</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>46163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45706</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46164</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45982</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46164</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45982</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45600</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45985</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45548</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45062</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46165</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45394</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45327</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45936</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46112</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45992</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45750</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46168</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46035</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46097</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45995</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45999</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46001</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45461</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46001</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45527</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>44651</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46007</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>46174</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>46174</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>46174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45796</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>46008</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>46174</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45028</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44508</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44649</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45012</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45622</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45622</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46026</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46174</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46174</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46026</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46029</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45602</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45561</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46030</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45707</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46035</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46024</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46034</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>46035</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46175</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46024</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>46035</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>46024</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46037</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>46036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>46036</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>46037</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>46037</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46043</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>46177</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>46041</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45747</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>46043</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45762</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>46177</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45202</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>46045</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45604</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45775</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45764</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45467</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45027</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45210</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46055</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>46181</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>46052</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>46055</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>46055</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>46052</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45574</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>46058</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>46063</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>46062</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>46062</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45056</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>46063</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46063</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45621</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>46062</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46063</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>46066</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>46069</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>46066</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46188</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>46185</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>46066</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>46066</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>46069</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44963</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46070</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>46073</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45750</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>46077</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>46076</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>44957</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>46076</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46076</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>46076</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>46079</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45251</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>46085</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46085</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45246</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>44546</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46087</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46122</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45632</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>46093</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>46093</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>46062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>46094</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46098</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>46099</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>46099</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46099</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45593</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>46104</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45425</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45588</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>46106</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45565</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46108</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45566</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45757</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>46111</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>46112</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>46197</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>46112</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>46112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>46197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45707</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>44897</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>44869</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45246</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>46113</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46117</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>46117</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>46117</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>46117</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45616</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45222</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46094</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45398</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44490</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45275</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46127</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46133</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45324</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46132</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46132</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45219</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46135</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>46135</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>46029</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46093</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>46093</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>46136</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>46062</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>46087</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>46058</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45905</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>45470</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>46207</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45754</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45609</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>44564</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>46212</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46212</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>46212</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>46212</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>46211</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>46042</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45677</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45799</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45243</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46219</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46219</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>46219</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46219</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>46223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45215</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>46272</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45580</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46227</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45560</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45560</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45107</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>44992</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44760</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>46275</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45764</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45278</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45453</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>44739</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46281</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46048</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46237</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>44582</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45747</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45544</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45093</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>46147</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45722</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44956</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45560</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45639</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44992</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45477</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45096</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>46026</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45108</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45476</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45597</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45432</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44823</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45602</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45770</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45108</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45609</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45595</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45771</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>46293</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45590</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45705</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45327</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>46293</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>46293</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45435</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>46163</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>46078</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>46252</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>46252</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>46294</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>46294</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45534</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45594</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43086,7 +43086,7 @@
         <v>45764</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45113</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>46296</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46296</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>46295</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46296</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>46253</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>46296</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>46253</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>46085</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46155</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45600</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>46301</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>46177</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45749</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>45779</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>46258</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45544</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>45588</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45149</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45420</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>46303</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>46303</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>46302</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>46034</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>45791</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45791</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45791</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>46303</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>46034</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46303</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>46260</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>44698</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45527</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45442</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45467</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>44776</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45798</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46304</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>46304</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>45799</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45643</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45428</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>46309</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>45805</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45272</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>44883</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45810</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>46310</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>46310</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>46268</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45762</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>46311</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>46310</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46218</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45821</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45824</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45824</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>46310</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45826</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45825</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>45600</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45436</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45817</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45847</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45848</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45848</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45863</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45867</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45811</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45879</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45879</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45821</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45293</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>44566</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>44566</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>44566</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45973</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>46070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>46162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>46168</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>46296</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45425</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45293</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45617</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45569</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>44826</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45891</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45884</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>45972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45440</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>45509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45554</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45992</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45994</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45994</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45632</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45632</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46052</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>46070</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44580</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45632</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>46052</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45035</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>46085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45825</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45293</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44686</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44837</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44740</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44740</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44783</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44820</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44837</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44663</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44838</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44698</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44491</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44750</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>45267</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45107</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44907</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>45428</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45764</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45471</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44937</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45443</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44846</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44992</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45365</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45750</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45432</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45595</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45597</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44665</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45212</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45264</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44795</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45251</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45069</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45673</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>45008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45425</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45425</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45108</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45108</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45331</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45257</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45230</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45107</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45666</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45084</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45632</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44543</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44826</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>46132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45791</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46041</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46041</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>46036</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46044</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>46050</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44757</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45639</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>46139</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45342</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45891</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45891</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45890</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45890</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44856</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>46043</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45896</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45698</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>46085</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45884</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45898</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45558</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45960</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46066</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>46087</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>46024</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>46097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45899</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>45461</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>46108</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>46043</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45762</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>46030</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>46098</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45905</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45215</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45905</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45632</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45632</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45632</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45296</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45757</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45632</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>46142</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>46142</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>46146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45972</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>46024</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45548</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44662</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45747</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45342</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>46147</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>46141</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>46146</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46149</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45279</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45580</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>46148</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46148</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46149</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>45929</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>46087</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45597</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45040</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>46150</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45936</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45937</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45254</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>44837</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45562</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45393</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45243</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45943</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45093</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45944</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45677</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45545</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>46076</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45510</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46155</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45754</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45398</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45954</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>46155</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>46157</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46157</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46157</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46157</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>46157</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>46157</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>46101</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46157</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45960</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45960</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45960</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45426</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45597</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45967</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45966</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45967</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45966</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45972</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>46163</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45975</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45761</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>45615</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45748</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45670</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45974</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45526</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45597</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45961</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>44938</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>46162</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>46163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45706</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46164</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45982</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46164</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45982</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45600</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45985</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45548</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45062</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46165</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45394</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45327</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45936</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46112</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45992</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45750</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46168</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46035</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46097</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45995</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45999</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46001</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45461</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46001</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45527</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>44651</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46007</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>46174</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>46174</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>46174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45796</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>46008</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>46174</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45028</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44508</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44649</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45012</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45622</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45622</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46026</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46174</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46174</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46026</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46029</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45602</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45561</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46030</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45707</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46035</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46024</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46034</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>46035</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46175</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46024</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>46035</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>46024</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46037</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>46036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>46036</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>46037</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>46037</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46043</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>46177</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>46041</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45747</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>46043</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45762</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>46177</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45202</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>46045</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45604</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45775</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45764</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45467</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45027</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45210</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46055</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>46181</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>46052</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>46055</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>46055</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>46052</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45574</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>46058</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>46063</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>46062</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>46062</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45056</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>46063</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46063</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45621</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>46062</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46063</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>46066</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>46069</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>46066</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46188</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>46185</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>46066</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>46066</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>46069</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44963</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46070</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>46073</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45750</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>46077</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>46076</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>44957</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>46076</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46076</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>46076</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>46079</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45251</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>46085</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46085</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45246</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>44546</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46087</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46122</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45632</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>46093</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>46093</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>46062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>46094</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46098</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46099</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>46099</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>46099</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46099</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45593</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>46104</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45425</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45588</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>46106</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45565</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46108</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45566</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45757</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>46111</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>46112</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>46197</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>46112</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>46112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>46197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45707</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>44897</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>44869</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45246</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>46113</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46117</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>46117</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>46117</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>46117</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45616</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45222</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46094</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45398</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44490</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45275</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46127</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46133</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45324</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>46132</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46132</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45219</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46135</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>46135</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>46029</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46093</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>46093</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>46136</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>46062</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>46087</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>46058</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45905</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>45470</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>46207</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45754</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45609</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>44564</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>46212</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46212</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>46212</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>46212</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>46211</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>46042</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45677</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45799</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45243</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46219</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46219</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>46219</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46219</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>46223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45215</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>46272</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45580</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46227</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45560</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45560</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45107</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>44992</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44760</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>46275</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45764</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45278</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45453</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>44739</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46281</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46048</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>46237</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>44582</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45747</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45544</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45093</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>46147</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45722</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44956</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45560</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45639</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44992</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45477</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45096</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>46026</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45108</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45476</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45597</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45432</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44823</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45602</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45770</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45108</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45609</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45595</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45771</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>46293</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45590</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45705</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45327</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>46293</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>46293</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45435</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>46163</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>46078</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>46252</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>46252</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>46294</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>46294</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45534</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45594</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43086,7 +43086,7 @@
         <v>45764</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45113</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>46296</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46296</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>46295</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46296</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>46253</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>46296</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>46253</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>46085</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46155</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45600</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>46301</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>46177</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45749</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>45779</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>46258</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45544</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>45588</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45149</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45420</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         <v>46303</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>46303</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>46302</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>46034</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>45791</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45791</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45791</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>46303</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>46034</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46303</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>46260</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>44698</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45527</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45442</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45467</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>44776</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45798</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46304</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>46304</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>45799</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>45643</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45428</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>46309</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>45805</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45272</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>44883</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45810</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>46310</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>46310</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>46268</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45762</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>46311</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>46310</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46218</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45821</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45824</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45824</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>46310</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45826</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45825</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>45600</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45436</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45817</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45847</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45848</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45848</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45863</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45867</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45811</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45879</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45879</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45821</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45293</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>44566</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>44566</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>44566</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45973</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>46168</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45425</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46296</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45293</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44580</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45632</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45947</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45617</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45509</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45629</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45569</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45992</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45994</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45440</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46052</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45825</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>46085</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>45972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45035</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45554</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45632</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45632</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44826</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45293</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44783</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44508</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44686</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>44837</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>44824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44637</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44823</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44740</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44823</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44841</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44867</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44546</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44663</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44838</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>44957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45215</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45890</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45698</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>45890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>45889</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45891</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45891</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45327</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45883</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45898</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>45183</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44856</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45775</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45342</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44665</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45754</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44651</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45762</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45899</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45884</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45108</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45905</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>46157</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>46157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45041</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>46162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>44963</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45764</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45231</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45911</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>46164</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>46164</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45597</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>46163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45243</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45632</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45632</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45470</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46167</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44543</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46165</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45891</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45278</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>46112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>46035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>46168</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>46097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45929</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45929</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45342</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45632</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45747</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45936</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45600</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45750</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>46174</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>46175</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>46174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>46174</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45944</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>46174</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>46174</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>46174</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45428</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45943</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>46177</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>46177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44508</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44823</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>46043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45527</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45425</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45254</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45210</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45435</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45628</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45677</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>46182</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45673</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45957</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45957</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>46185</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45771</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45960</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>46122</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45098</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46188</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45966</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45966</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44826</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45588</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45580</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45252</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>45967</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45215</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45971</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46062</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45108</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>46197</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45595</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45595</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45394</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>46197</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45770</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45750</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45961</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45622</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45979</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45219</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45979</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45748</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45069</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45982</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45296</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45985</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>46207</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45327</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>46211</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>45992</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44546</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45992</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45992</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45707</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46212</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46212</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46212</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>46212</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45632</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45995</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45615</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45999</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>46219</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>46219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45265</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45999</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45999</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46219</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>46219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>46000</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46223</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>46001</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45779</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>46227</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45420</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46007</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45278</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45588</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45796</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>46237</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>46147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45544</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45149</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46026</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46026</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>46029</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45791</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46030</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46024</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45791</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45707</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46024</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>46034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>46026</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45791</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>46036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>46035</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>46035</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>46024</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>46035</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>46037</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>46037</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>46037</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45527</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45442</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44698</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>46041</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>46043</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45643</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45798</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46044</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44776</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45467</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45597</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>46045</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46052</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45428</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45545</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45545</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>46052</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45805</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46055</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46055</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>44883</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45279</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>46058</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45810</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>46062</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45762</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>46062</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46062</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46078</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46063</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>46063</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46063</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>46294</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46066</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46066</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46066</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46069</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46293</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>46070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46293</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46293</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>46069</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46163</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45467</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>46076</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46076</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46076</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45821</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46073</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45824</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>46076</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45824</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>46077</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>46296</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46252</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45443</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>46296</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45825</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>46253</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>46296</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45600</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>46296</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>46085</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>46087</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46253</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>46093</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45012</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45544</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46093</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46094</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>46295</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>46099</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>46099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>46098</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46099</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>46099</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45436</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>46155</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>46104</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45817</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46104</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45432</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45848</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46302</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46301</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45847</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45848</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46034</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46177</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46108</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45757</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>46111</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>46258</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46258</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>46112</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>46113</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46112</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46303</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>46034</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45863</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45811</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46117</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45246</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46117</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46117</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>46117</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45867</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45471</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46303</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>46304</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46260</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>46094</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>46303</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>46260</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>46127</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46304</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>46303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46132</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45879</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45879</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45821</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45275</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46132</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45398</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>46133</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>46093</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45545</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44897</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>46135</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46135</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45476</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>46093</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45566</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>46029</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45905</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>46310</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>46309</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46310</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46058</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>46267</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>46062</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>46310</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45604</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>46310</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46108</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46087</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46087</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>46218</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46041</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46314</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46041</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46132</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45748</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46268</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46311</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46066</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45960</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45817</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45558</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44582</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>46036</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45791</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>46315</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45757</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>46044</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>44937</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44869</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45971</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46024</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45107</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>46043</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>46043</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>46085</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>46136</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>46050</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>46139</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45260</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>46317</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46030</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46317</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>46098</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46275</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45324</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>46142</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46142</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46097</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45594</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46024</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46317</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46318</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>46146</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45548</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45972</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46146</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>46141</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46148</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>46148</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>46147</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46087</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46149</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>46150</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46149</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45398</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46149</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45526</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45093</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45251</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>46155</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46155</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46076</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46101</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>46157</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46157</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44956</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46157</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46157</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>46157</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45426</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>45574</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45609</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45609</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45621</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45597</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45754</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45548</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45632</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>44649</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>44757</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>44795</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>45666</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45722</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45764</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45246</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45219</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44837</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45705</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44739</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45749</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>44824</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45670</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45762</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>44846</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45677</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45243</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45170</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45750</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45750</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>44760</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45113</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44895</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45202</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45764</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45453</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45636</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45251</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45264</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>44992</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>44907</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45084</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45107</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45560</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45560</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45093</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>45574</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45107</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45062</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45600</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45096</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45028</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>45461</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>44938</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>45040</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45593</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45616</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45212</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45761</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45365</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45108</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45108</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>44564</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>45027</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45607</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45622</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45580</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45670</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45754</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>45056</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45615</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45590</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45632</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45639</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45597</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45706</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45747</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45331</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>44812</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45597</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45222</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45639</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45432</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45113</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>45705</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45670</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45188</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>44662</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>44750</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45764</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45257</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45267</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>45477</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45602</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45652</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45393</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45510</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45461</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45425</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>45749</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45534</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45561</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>44992</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45560</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>44992</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>44566</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>44566</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44566</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45293</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45973</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt SÖDERHAMN.xlsx
+++ b/Översikt SÖDERHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45393</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45331</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44706</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44523</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45509</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45798</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>46168</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45425</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46296</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45293</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44580</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45632</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45947</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45617</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45509</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45629</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45569</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45992</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45994</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45440</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46052</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45825</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>46085</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>45972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45035</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45554</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45632</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45632</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44826</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45293</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44783</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44508</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44686</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>44837</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>44824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44637</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44740</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44823</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44740</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44823</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44841</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44867</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44546</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44663</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44838</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>44957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45215</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45890</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45698</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>45890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>45889</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45891</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45891</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45327</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45883</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45898</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>45183</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44856</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45775</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45342</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44665</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45754</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44651</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45762</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45899</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45884</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45108</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45905</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>46157</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>46157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45041</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>46162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>44963</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45764</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45231</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45911</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>46164</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>46164</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45597</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>46163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45243</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45632</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45632</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45470</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46167</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44543</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46165</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45891</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45278</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>46112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>46035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>46168</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>46097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45929</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45929</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45342</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45632</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45747</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45936</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45600</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45750</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>46174</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>46175</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>46174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>46174</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45944</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>46174</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>46174</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>46174</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45428</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45943</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>46177</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>46177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44508</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44823</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>46043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45527</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45425</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45254</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45210</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45435</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45628</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45677</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>46182</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45673</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45957</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45957</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>46185</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45771</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45960</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>46122</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45098</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46188</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45966</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45966</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44826</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45588</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45580</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45252</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>45967</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45215</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45971</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46062</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45108</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>46197</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45595</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45595</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45394</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>46197</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45770</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45750</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45961</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45622</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45979</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45219</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45979</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45748</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45069</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45982</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45296</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45985</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>46207</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45327</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>46211</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>45992</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44546</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45992</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45992</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45707</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46212</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46212</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46212</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>46212</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45632</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45995</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45615</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45999</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>46219</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>46219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45265</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45999</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45999</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46219</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>46219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>46000</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46223</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>46001</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45779</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>46227</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45420</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46007</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45278</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45588</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45796</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>46237</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>46147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45544</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45149</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46026</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46026</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>46029</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45791</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46030</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46024</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45791</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45707</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46024</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>46034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>46026</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45791</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>46036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>46035</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>46035</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>46024</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>46035</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>46037</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>46037</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>46037</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45527</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45442</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44698</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>46041</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>46043</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45643</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45798</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46044</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44776</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45467</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45597</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>46045</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46052</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45428</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45545</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45545</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>46052</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45805</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46055</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46055</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>44883</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45279</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>46058</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45810</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>46062</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45762</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>46062</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46062</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46078</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46063</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>46063</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46063</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>46294</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46066</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46066</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46066</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46069</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46293</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>46070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46293</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46293</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>46069</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46163</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45467</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>46076</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46076</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46076</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45821</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46073</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45824</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>46076</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45824</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>46077</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>46296</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46252</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45443</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>46296</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45825</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>46253</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>46296</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45600</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>46296</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>46085</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>46087</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46253</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>46093</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45012</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45544</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46093</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46094</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>46295</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>46099</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>46099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>46098</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46099</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>46099</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45436</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>46155</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>46104</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45817</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46104</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45432</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45848</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46302</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46301</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45847</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45848</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>46034</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46177</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46108</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45757</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>46111</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>46258</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46258</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>46112</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>46113</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46112</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46303</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>46034</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45863</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45811</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46117</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45246</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46117</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46117</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>46117</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45867</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45471</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46303</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>46304</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46260</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>46094</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>46303</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>46260</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>46127</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46304</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>46303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46132</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45879</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45879</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45821</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45275</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46132</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45398</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>46133</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>46093</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45545</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44897</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>46135</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46135</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45476</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>46093</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45566</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>46029</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45905</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>46310</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>46309</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46310</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46058</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>46267</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>46062</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>46310</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45604</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>46310</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46108</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46087</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46087</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>46218</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46041</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46314</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46041</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46132</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45748</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46268</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46311</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46066</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45960</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45817</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45558</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44582</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>46036</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45791</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>46315</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>45757</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>46044</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>44937</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44869</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45971</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46024</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45107</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>46043</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>46043</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>46085</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>46136</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>46050</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>46139</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45260</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>46317</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46030</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46317</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>46098</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46275</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45324</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>46142</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46142</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46097</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45594</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46024</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46317</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46318</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>46146</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45548</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45972</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46146</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>46141</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46148</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>46148</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>46147</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46087</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46149</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>46150</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46149</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45398</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46149</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45526</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45093</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45251</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>46155</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46155</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46076</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46101</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>46157</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46157</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44956</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46157</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46157</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>46157</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45426</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>45574</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45609</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45609</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45621</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45597</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45754</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45548</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45632</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>44649</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>44757</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>44795</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>45666</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45722</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45764</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45246</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45219</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44837</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45705</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44739</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45749</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>44824</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45670</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45762</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>44846</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45677</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45243</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45170</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45750</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45750</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>44760</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45113</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44895</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45202</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45764</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45453</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45636</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45251</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45264</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>44992</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>44907</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45084</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45107</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45560</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45560</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45093</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>45574</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>45107</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45062</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45600</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45096</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45028</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>45461</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>44938</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>45040</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45593</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45616</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45212</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45761</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45365</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45108</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45108</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>44564</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>45027</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45607</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45622</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45580</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45670</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45754</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>45056</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45615</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45590</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45632</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45639</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45597</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45706</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45747</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45331</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>44812</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45597</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45222</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45639</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45432</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45113</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>45705</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45670</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45188</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>44662</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>44750</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45764</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45257</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45267</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>45477</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45602</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45652</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45393</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45510</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45461</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45425</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>45749</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45534</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45561</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>44992</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45560</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>44992</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>44566</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>44566</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44566</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45293</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45973</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
